--- a/outputs/marine_equipment/Контейнер_40ф_Питер.xlsx
+++ b/outputs/marine_equipment/Контейнер_40ф_Питер.xlsx
@@ -11,7 +11,8 @@
     <sheet name="Контейнер 40 футов" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Остается" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Ящики и места" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Упаковка и крепление" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Лес на перекладку" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Упаковка и крепление" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Контейнер 40 футов'!$A$4:$Q$310</definedName>
@@ -134,7 +135,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -198,6 +199,7 @@
     <xf numFmtId="3" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -29248,6 +29250,280 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Сколько доски купить</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Доска необрезная 25 мм. Пол контейнера 12.03 x 2.35 = 28.3 кв. м. Количество считано по площади настилов с запасом 25% на обзол и подгонку.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Клинкеты Ду200 и выше</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>55 шт</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>7.63 т</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Их пятно на полу</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>11.5 кв. м</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>40% пола — ложатся одним слоем, второй ярус клинкетов не нужен</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Ящиков</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>23 шт</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>1200 x 1000 x 910 мм, на поддоне</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Куда идет доска</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Площадь, кв. м</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Пояснение</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>Настил на пол под клинкеты</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="C9" s="15" t="inlineStr">
+        <is>
+          <t>сплошной, чтобы задвижка стояла на доске, а не на рифленом железе</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>Настил поверх клинкетов</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="C10" s="15" t="inlineStr">
+        <is>
+          <t>по нему встают ящики, доска ложится над корпусами, а не над маховиками</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>Прокладки внутри ящиков</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="C11" s="15" t="inlineStr">
+        <is>
+          <t>23 ящиков, по два прокладочных ряда, доской закрыта примерно треть площади</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="14" t="inlineStr">
+        <is>
+          <t>Распорки, клинья, подгонка</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="C12" s="15" t="inlineStr">
+        <is>
+          <t>десятая часть от настилов</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>ИТОГО площадь настилов</t>
+        </is>
+      </c>
+      <c r="B13" s="10">
+        <f>SUM(B9:B12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Сколько это в лесе</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Чистый объем доски, куб. м</t>
+        </is>
+      </c>
+      <c r="B16" s="29" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>43.4 кв. м настила толщиной 25 мм</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>С запасом на обзол и подгонку, куб. м</t>
+        </is>
+      </c>
+      <c r="B17" s="29" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>коэффициент 1.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Доска 4 м, средняя ширина 20 см</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>68 шт</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>одна доска закрывает 0.8 кв. м</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Погонных метров</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>272 м</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Что еще купить</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="17" t="inlineStr">
+        <is>
+          <t>— Поддоны под ящики — 23 штук плюс запас на бой.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="17" t="inlineStr">
+        <is>
+          <t>— Брус 50х50 на каркас ящиков: по четырем углам и по верхней обвязке. Без него ящик на 600 кг складывается от первого же удара на маневрировании.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="17" t="inlineStr">
+        <is>
+          <t>— Стяжные ремни для крепления к рымам и фанера на заглушки фланцев.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" s="17" t="inlineStr">
+        <is>
+          <t>— Необрезную доску берут нестроганой и невысушенной — для перекладки это нормально, но сырая доска тяжелее: 1.4 куб. м это около 950 кг к весу контейнера. Это надо учесть в лимите.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>

--- a/outputs/marine_equipment/Контейнер_40ф_Питер.xlsx
+++ b/outputs/marine_equipment/Контейнер_40ф_Питер.xlsx
@@ -10,9 +10,10 @@
     <sheet name="Сводка" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Контейнер 40 футов" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Остается" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Ящики и места" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Лес на перекладку" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Упаковка и крепление" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Укладка и нагрузка" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Ящики и места" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Лес на перекладку" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Упаковка и крепление" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Контейнер 40 футов'!$A$4:$Q$310</definedName>
@@ -24,10 +25,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="#,##0.0"/>
     <numFmt numFmtId="166" formatCode="#,##0.000"/>
+    <numFmt numFmtId="167" formatCode="#,##0.0000"/>
   </numFmts>
   <fonts count="7">
     <font>
@@ -135,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -190,6 +192,12 @@
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
@@ -20130,6 +20138,867 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E59"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Укладка: клинкеты в один слой, нагрузка на нижний ряд</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Сорокафутовый берет все клинкеты одним слоем: они просят 10.70 м пола при длине 12.032 м. Задвижка на задвижку не кладется, и это главное отличие от двадцатифутового.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Нижний ярус: клинкеты</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="26" t="inlineStr">
+        <is>
+          <t>Клинкетов, шт</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="n">
+        <v>55</v>
+      </c>
+      <c r="C5" s="2" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="26" t="inlineStr">
+        <is>
+          <t>Рядов поперек контейнера</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="n">
+        <v>26</v>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Ду350 и Ду300 по 2 в ряд, Ду250 по 2, Ду200 по 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="26" t="inlineStr">
+        <is>
+          <t>Просят пола, м</t>
+        </is>
+      </c>
+      <c r="B7" s="27" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>пол 12.032 м</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="26" t="inlineStr">
+        <is>
+          <t>СЛОЕВ КЛИНКЕТОВ</t>
+        </is>
+      </c>
+      <c r="B8" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>один слой — задвижка на задвижку не ложится</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="26" t="inlineStr">
+        <is>
+          <t>Остается свободного пола, м</t>
+        </is>
+      </c>
+      <c r="B9" s="27" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>это 3.1 кв. м</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="26" t="inlineStr">
+        <is>
+          <t>Высота пирога клинкетов с досками, м</t>
+        </is>
+      </c>
+      <c r="B10" s="27" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>до потолка 1.82 м</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="26" t="inlineStr">
+        <is>
+          <t>Ярусов ящиков встает сверху</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C11" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Ряд за рядом</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Ряд</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Что кладем</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Штук в ряду</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>Глубина ряда, м</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>Нарастающим, м</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>Клинкет Ду350</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E15" s="29" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>Клинкет Ду300</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" s="29" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E16" s="29" t="n">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>Клинкет Ду300</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" s="29" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E17" s="29" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>Клинкет Ду300</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" s="29" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E18" s="29" t="n">
+        <v>1.85</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>Клинкет Ду300</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" s="29" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E19" s="29" t="n">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>Клинкет Ду300</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" s="29" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E20" s="29" t="n">
+        <v>2.75</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>Клинкет Ду300</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" s="29" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E21" s="29" t="n">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>Клинкет Ду300</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" s="29" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E22" s="29" t="n">
+        <v>3.65</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>Клинкет Ду300</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" s="29" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E23" s="29" t="n">
+        <v>4.1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>Клинкет Ду300</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D24" s="29" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E24" s="29" t="n">
+        <v>4.55</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>Клинкет Ду250</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D25" s="29" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E25" s="29" t="n">
+        <v>4.95</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>Клинкет Ду250</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D26" s="29" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E26" s="29" t="n">
+        <v>5.35</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>Клинкет Ду250</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D27" s="29" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E27" s="29" t="n">
+        <v>5.75</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>Клинкет Ду250</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D28" s="29" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E28" s="29" t="n">
+        <v>6.15</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>Клинкет Ду250</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D29" s="29" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E29" s="29" t="n">
+        <v>6.55</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>Клинкет Ду250</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D30" s="29" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E30" s="29" t="n">
+        <v>6.95</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>Клинкет Ду250</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D31" s="29" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E31" s="29" t="n">
+        <v>7.35</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>Клинкет Ду250</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D32" s="29" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E32" s="29" t="n">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>Клинкет Ду250</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D33" s="29" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E33" s="29" t="n">
+        <v>8.15</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>Клинкет Ду250</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D34" s="29" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E34" s="29" t="n">
+        <v>8.550000000000001</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>Клинкет Ду250</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" s="29" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E35" s="29" t="n">
+        <v>8.949999999999999</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>Клинкет Ду200</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D36" s="29" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E36" s="29" t="n">
+        <v>9.300000000000001</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>Клинкет Ду200</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D37" s="29" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E37" s="29" t="n">
+        <v>9.65</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>Клинкет Ду200</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D38" s="29" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E38" s="29" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>Клинкет Ду200</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D39" s="29" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E39" s="29" t="n">
+        <v>10.35</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="n">
+        <v>26</v>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>Клинкет Ду200</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D40" s="29" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E40" s="29" t="n">
+        <v>10.7</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Фильтры и ящики</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="26" t="inlineStr">
+        <is>
+          <t>Крупных фильтров Ду200 и выше, шт</t>
+        </is>
+      </c>
+      <c r="B43" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>1356 кг</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="26" t="inlineStr">
+        <is>
+          <t>Просят пола, кв. м</t>
+        </is>
+      </c>
+      <c r="B44" s="10" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>свободно 3.1 кв. м</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="26" t="inlineStr">
+        <is>
+          <t>Ставим их на пол</t>
+        </is>
+      </c>
+      <c r="B45" s="30" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>на свободную полосу, а не поверх ящиков: они тяжелые, и наверху это лишний груз и центр тяжести</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="26" t="inlineStr">
+        <is>
+          <t>Мелкие фильтры и титан в ящики, кг</t>
+        </is>
+      </c>
+      <c r="B46" s="9" t="n">
+        <v>858</v>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>два яруса ящиков упираются в потолок, сверху места нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="26" t="inlineStr">
+        <is>
+          <t>Ящиков с мелочью</t>
+        </is>
+      </c>
+      <c r="B47" s="9" t="n">
+        <v>21</v>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>по 600 кг, всего в ящиках 12129 кг</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="26" t="inlineStr">
+        <is>
+          <t>Мест под ящики поверх клинкетов</t>
+        </is>
+      </c>
+      <c r="B48" s="9" t="n">
+        <v>32</v>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>2 яруса</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="26" t="inlineStr">
+        <is>
+          <t>Ящиков встанет на клинкеты</t>
+        </is>
+      </c>
+      <c r="B49" s="9" t="n">
+        <v>21</v>
+      </c>
+      <c r="C49" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Нагрузка на нижний ярус</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="26" t="inlineStr">
+        <is>
+          <t>Вес поверх клинкетов, кг</t>
+        </is>
+      </c>
+      <c r="B52" s="9" t="n">
+        <v>12129</v>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>только ящики: крупные фильтры сняты на пол</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="26" t="inlineStr">
+        <is>
+          <t>Площадь под клинкетами, кв. м</t>
+        </is>
+      </c>
+      <c r="B53" s="9" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="C53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="26" t="inlineStr">
+        <is>
+          <t>Нагрузка, кг на кв. м</t>
+        </is>
+      </c>
+      <c r="B54" s="9" t="n">
+        <v>482</v>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>в двух двадцатифутовых выходит 511 и 631, в усиленном клинкеты лежат в два слоя</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="26" t="inlineStr">
+        <is>
+          <t>В мегапаскалях</t>
+        </is>
+      </c>
+      <c r="B55" s="31" t="n">
+        <v>0.0047</v>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>бронза держит около 200 МПа, запас в десятки тысяч раз</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="44" customHeight="1">
+      <c r="A57" s="17" t="inlineStr">
+        <is>
+          <t>— Корпус задвижки такую нагрузку не замечает. Беречь надо шток, маховик и привалочную поверхность фланца: кладем на бок штоком горизонтально, съемные маховики снимаем в ящик с биркой, фланец на фланец не кладем.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="44" customHeight="1">
+      <c r="A58" s="17" t="inlineStr">
+        <is>
+          <t>— Прокладки под ящиками — строго над корпусами задвижек, шаг 300-400 мм. Доска 200 х 25 на пролете 600 мм выходит на предел по изгибу, под угол ящика над пустотой ставим брус 50 х 50.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="44" customHeight="1">
+      <c r="A59" s="17" t="inlineStr">
+        <is>
+          <t>— Свободная полоса у двери — это и запас на распорки. Пустоты забиваем, месяц дороги дает продольные удары.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I316"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -20291,31 +21160,31 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="26" t="inlineStr">
+      <c r="A11" s="32" t="inlineStr">
         <is>
           <t>ЯЩИК 1</t>
         </is>
       </c>
-      <c r="B11" s="26" t="inlineStr">
+      <c r="B11" s="32" t="inlineStr">
         <is>
           <t>Нижний ярус ящиков</t>
         </is>
       </c>
-      <c r="C11" s="27" t="inlineStr">
+      <c r="C11" s="33" t="inlineStr">
         <is>
           <t>Штуцерная проходная</t>
         </is>
       </c>
-      <c r="D11" s="26" t="n"/>
-      <c r="E11" s="26" t="n"/>
-      <c r="F11" s="26" t="n"/>
-      <c r="G11" s="26" t="n">
+      <c r="D11" s="32" t="n"/>
+      <c r="E11" s="32" t="n"/>
+      <c r="F11" s="32" t="n"/>
+      <c r="G11" s="32" t="n">
         <v>500</v>
       </c>
-      <c r="H11" s="28" t="n">
+      <c r="H11" s="34" t="n">
         <v>600</v>
       </c>
-      <c r="I11" s="26" t="n">
+      <c r="I11" s="32" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -20351,31 +21220,31 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="26" t="inlineStr">
+      <c r="A13" s="32" t="inlineStr">
         <is>
           <t>ЯЩИК 2</t>
         </is>
       </c>
-      <c r="B13" s="26" t="inlineStr">
+      <c r="B13" s="32" t="inlineStr">
         <is>
           <t>Нижний ярус ящиков</t>
         </is>
       </c>
-      <c r="C13" s="27" t="inlineStr">
+      <c r="C13" s="33" t="inlineStr">
         <is>
           <t>Штуцерная проходная</t>
         </is>
       </c>
-      <c r="D13" s="26" t="n"/>
-      <c r="E13" s="26" t="n"/>
-      <c r="F13" s="26" t="n"/>
-      <c r="G13" s="26" t="n">
+      <c r="D13" s="32" t="n"/>
+      <c r="E13" s="32" t="n"/>
+      <c r="F13" s="32" t="n"/>
+      <c r="G13" s="32" t="n">
         <v>311</v>
       </c>
-      <c r="H13" s="28" t="n">
+      <c r="H13" s="34" t="n">
         <v>600</v>
       </c>
-      <c r="I13" s="26" t="n">
+      <c r="I13" s="32" t="n">
         <v>0.64</v>
       </c>
     </row>
@@ -21058,31 +21927,31 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="26" t="inlineStr">
+      <c r="A36" s="32" t="inlineStr">
         <is>
           <t>ЯЩИК 3</t>
         </is>
       </c>
-      <c r="B36" s="26" t="inlineStr">
+      <c r="B36" s="32" t="inlineStr">
         <is>
           <t>Нижний ярус ящиков</t>
         </is>
       </c>
-      <c r="C36" s="27" t="inlineStr">
+      <c r="C36" s="33" t="inlineStr">
         <is>
           <t>Штуцерная проходная, Штуцерная угловая</t>
         </is>
       </c>
-      <c r="D36" s="26" t="n"/>
-      <c r="E36" s="26" t="n"/>
-      <c r="F36" s="26" t="n"/>
-      <c r="G36" s="26" t="n">
+      <c r="D36" s="32" t="n"/>
+      <c r="E36" s="32" t="n"/>
+      <c r="F36" s="32" t="n"/>
+      <c r="G36" s="32" t="n">
         <v>368</v>
       </c>
-      <c r="H36" s="28" t="n">
+      <c r="H36" s="34" t="n">
         <v>599</v>
       </c>
-      <c r="I36" s="26" t="n">
+      <c r="I36" s="32" t="n">
         <v>0.63</v>
       </c>
     </row>
@@ -21602,31 +22471,31 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="26" t="inlineStr">
+      <c r="A54" s="32" t="inlineStr">
         <is>
           <t>ЯЩИК 4</t>
         </is>
       </c>
-      <c r="B54" s="26" t="inlineStr">
+      <c r="B54" s="32" t="inlineStr">
         <is>
           <t>Нижний ярус ящиков</t>
         </is>
       </c>
-      <c r="C54" s="27" t="inlineStr">
+      <c r="C54" s="33" t="inlineStr">
         <is>
           <t>Штуцерная проходная</t>
         </is>
       </c>
-      <c r="D54" s="26" t="n"/>
-      <c r="E54" s="26" t="n"/>
-      <c r="F54" s="26" t="n"/>
-      <c r="G54" s="26" t="n">
+      <c r="D54" s="32" t="n"/>
+      <c r="E54" s="32" t="n"/>
+      <c r="F54" s="32" t="n"/>
+      <c r="G54" s="32" t="n">
         <v>307</v>
       </c>
-      <c r="H54" s="28" t="n">
+      <c r="H54" s="34" t="n">
         <v>599</v>
       </c>
-      <c r="I54" s="26" t="n">
+      <c r="I54" s="32" t="n">
         <v>0.47</v>
       </c>
     </row>
@@ -22704,31 +23573,31 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="26" t="inlineStr">
+      <c r="A90" s="32" t="inlineStr">
         <is>
           <t>ЯЩИК 5</t>
         </is>
       </c>
-      <c r="B90" s="26" t="inlineStr">
+      <c r="B90" s="32" t="inlineStr">
         <is>
           <t>Нижний ярус ящиков</t>
         </is>
       </c>
-      <c r="C90" s="27" t="inlineStr">
+      <c r="C90" s="33" t="inlineStr">
         <is>
           <t>Паровые клапаны, Педальные клапаны, Редукционные клапаны, Электромагнитные клапаны</t>
         </is>
       </c>
-      <c r="D90" s="26" t="n"/>
-      <c r="E90" s="26" t="n"/>
-      <c r="F90" s="26" t="n"/>
-      <c r="G90" s="26" t="n">
+      <c r="D90" s="32" t="n"/>
+      <c r="E90" s="32" t="n"/>
+      <c r="F90" s="32" t="n"/>
+      <c r="G90" s="32" t="n">
         <v>64</v>
       </c>
-      <c r="H90" s="28" t="n">
+      <c r="H90" s="34" t="n">
         <v>598</v>
       </c>
-      <c r="I90" s="26" t="n">
+      <c r="I90" s="32" t="n">
         <v>0.24</v>
       </c>
     </row>
@@ -22967,31 +23836,31 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="26" t="inlineStr">
+      <c r="A99" s="32" t="inlineStr">
         <is>
           <t>ЯЩИК 6</t>
         </is>
       </c>
-      <c r="B99" s="26" t="inlineStr">
+      <c r="B99" s="32" t="inlineStr">
         <is>
           <t>Нижний ярус ящиков</t>
         </is>
       </c>
-      <c r="C99" s="27" t="inlineStr">
+      <c r="C99" s="33" t="inlineStr">
         <is>
           <t>Штуцерная угловая</t>
         </is>
       </c>
-      <c r="D99" s="26" t="n"/>
-      <c r="E99" s="26" t="n"/>
-      <c r="F99" s="26" t="n"/>
-      <c r="G99" s="26" t="n">
+      <c r="D99" s="32" t="n"/>
+      <c r="E99" s="32" t="n"/>
+      <c r="F99" s="32" t="n"/>
+      <c r="G99" s="32" t="n">
         <v>216</v>
       </c>
-      <c r="H99" s="28" t="n">
+      <c r="H99" s="34" t="n">
         <v>597</v>
       </c>
-      <c r="I99" s="26" t="n">
+      <c r="I99" s="32" t="n">
         <v>0.72</v>
       </c>
     </row>
@@ -24317,31 +25186,31 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="26" t="inlineStr">
+      <c r="A143" s="32" t="inlineStr">
         <is>
           <t>ЯЩИК 7</t>
         </is>
       </c>
-      <c r="B143" s="26" t="inlineStr">
+      <c r="B143" s="32" t="inlineStr">
         <is>
           <t>Нижний ярус ящиков</t>
         </is>
       </c>
-      <c r="C143" s="27" t="inlineStr">
+      <c r="C143" s="33" t="inlineStr">
         <is>
           <t>Фланцевая проходная, Фланцевая угловая</t>
         </is>
       </c>
-      <c r="D143" s="26" t="n"/>
-      <c r="E143" s="26" t="n"/>
-      <c r="F143" s="26" t="n"/>
-      <c r="G143" s="26" t="n">
+      <c r="D143" s="32" t="n"/>
+      <c r="E143" s="32" t="n"/>
+      <c r="F143" s="32" t="n"/>
+      <c r="G143" s="32" t="n">
         <v>64</v>
       </c>
-      <c r="H143" s="28" t="n">
+      <c r="H143" s="34" t="n">
         <v>597</v>
       </c>
-      <c r="I143" s="26" t="n">
+      <c r="I143" s="32" t="n">
         <v>0.58</v>
       </c>
     </row>
@@ -24702,31 +25571,31 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="26" t="inlineStr">
+      <c r="A156" s="32" t="inlineStr">
         <is>
           <t>ЯЩИК 8</t>
         </is>
       </c>
-      <c r="B156" s="26" t="inlineStr">
+      <c r="B156" s="32" t="inlineStr">
         <is>
           <t>Нижний ярус ящиков</t>
         </is>
       </c>
-      <c r="C156" s="27" t="inlineStr">
+      <c r="C156" s="33" t="inlineStr">
         <is>
           <t>Фланцевая проходная</t>
         </is>
       </c>
-      <c r="D156" s="26" t="n"/>
-      <c r="E156" s="26" t="n"/>
-      <c r="F156" s="26" t="n"/>
-      <c r="G156" s="26" t="n">
+      <c r="D156" s="32" t="n"/>
+      <c r="E156" s="32" t="n"/>
+      <c r="F156" s="32" t="n"/>
+      <c r="G156" s="32" t="n">
         <v>65</v>
       </c>
-      <c r="H156" s="28" t="n">
+      <c r="H156" s="34" t="n">
         <v>596</v>
       </c>
-      <c r="I156" s="26" t="n">
+      <c r="I156" s="32" t="n">
         <v>0.78</v>
       </c>
     </row>
@@ -24785,31 +25654,31 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="26" t="inlineStr">
+      <c r="A159" s="32" t="inlineStr">
         <is>
           <t>ЯЩИК 9</t>
         </is>
       </c>
-      <c r="B159" s="26" t="inlineStr">
+      <c r="B159" s="32" t="inlineStr">
         <is>
           <t>Нижний ярус ящиков</t>
         </is>
       </c>
-      <c r="C159" s="27" t="inlineStr">
+      <c r="C159" s="33" t="inlineStr">
         <is>
           <t>Фланцевая угловая</t>
         </is>
       </c>
-      <c r="D159" s="26" t="n"/>
-      <c r="E159" s="26" t="n"/>
-      <c r="F159" s="26" t="n"/>
-      <c r="G159" s="26" t="n">
+      <c r="D159" s="32" t="n"/>
+      <c r="E159" s="32" t="n"/>
+      <c r="F159" s="32" t="n"/>
+      <c r="G159" s="32" t="n">
         <v>24</v>
       </c>
-      <c r="H159" s="28" t="n">
+      <c r="H159" s="34" t="n">
         <v>595</v>
       </c>
-      <c r="I159" s="26" t="n">
+      <c r="I159" s="32" t="n">
         <v>0.71</v>
       </c>
     </row>
@@ -24876,31 +25745,31 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="26" t="inlineStr">
+      <c r="A162" s="32" t="inlineStr">
         <is>
           <t>ЯЩИК 10</t>
         </is>
       </c>
-      <c r="B162" s="26" t="inlineStr">
+      <c r="B162" s="32" t="inlineStr">
         <is>
           <t>Нижний ярус ящиков</t>
         </is>
       </c>
-      <c r="C162" s="27" t="inlineStr">
+      <c r="C162" s="33" t="inlineStr">
         <is>
           <t>Фланцевая проходная</t>
         </is>
       </c>
-      <c r="D162" s="26" t="n"/>
-      <c r="E162" s="26" t="n"/>
-      <c r="F162" s="26" t="n"/>
-      <c r="G162" s="26" t="n">
+      <c r="D162" s="32" t="n"/>
+      <c r="E162" s="32" t="n"/>
+      <c r="F162" s="32" t="n"/>
+      <c r="G162" s="32" t="n">
         <v>51</v>
       </c>
-      <c r="H162" s="28" t="n">
+      <c r="H162" s="34" t="n">
         <v>595</v>
       </c>
-      <c r="I162" s="26" t="n">
+      <c r="I162" s="32" t="n">
         <v>0.61</v>
       </c>
     </row>
@@ -24959,31 +25828,31 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="26" t="inlineStr">
+      <c r="A165" s="32" t="inlineStr">
         <is>
           <t>ЯЩИК 11</t>
         </is>
       </c>
-      <c r="B165" s="26" t="inlineStr">
+      <c r="B165" s="32" t="inlineStr">
         <is>
           <t>Нижний ярус ящиков</t>
         </is>
       </c>
-      <c r="C165" s="27" t="inlineStr">
+      <c r="C165" s="33" t="inlineStr">
         <is>
           <t>Фланцевая проходная</t>
         </is>
       </c>
-      <c r="D165" s="26" t="n"/>
-      <c r="E165" s="26" t="n"/>
-      <c r="F165" s="26" t="n"/>
-      <c r="G165" s="26" t="n">
+      <c r="D165" s="32" t="n"/>
+      <c r="E165" s="32" t="n"/>
+      <c r="F165" s="32" t="n"/>
+      <c r="G165" s="32" t="n">
         <v>63</v>
       </c>
-      <c r="H165" s="28" t="n">
+      <c r="H165" s="34" t="n">
         <v>592</v>
       </c>
-      <c r="I165" s="26" t="n">
+      <c r="I165" s="32" t="n">
         <v>0.79</v>
       </c>
     </row>
@@ -25162,31 +26031,31 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="26" t="inlineStr">
+      <c r="A172" s="32" t="inlineStr">
         <is>
           <t>ЯЩИК 12</t>
         </is>
       </c>
-      <c r="B172" s="26" t="inlineStr">
+      <c r="B172" s="32" t="inlineStr">
         <is>
           <t>Нижний ярус ящиков</t>
         </is>
       </c>
-      <c r="C172" s="27" t="inlineStr">
+      <c r="C172" s="33" t="inlineStr">
         <is>
           <t>Фланцевая угловая</t>
         </is>
       </c>
-      <c r="D172" s="26" t="n"/>
-      <c r="E172" s="26" t="n"/>
-      <c r="F172" s="26" t="n"/>
-      <c r="G172" s="26" t="n">
+      <c r="D172" s="32" t="n"/>
+      <c r="E172" s="32" t="n"/>
+      <c r="F172" s="32" t="n"/>
+      <c r="G172" s="32" t="n">
         <v>55</v>
       </c>
-      <c r="H172" s="28" t="n">
+      <c r="H172" s="34" t="n">
         <v>588</v>
       </c>
-      <c r="I172" s="26" t="n">
+      <c r="I172" s="32" t="n">
         <v>0.66</v>
       </c>
     </row>
@@ -25857,31 +26726,31 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="26" t="inlineStr">
+      <c r="A195" s="32" t="inlineStr">
         <is>
           <t>ЯЩИК 13</t>
         </is>
       </c>
-      <c r="B195" s="26" t="inlineStr">
+      <c r="B195" s="32" t="inlineStr">
         <is>
           <t>Нижний ярус ящиков</t>
         </is>
       </c>
-      <c r="C195" s="27" t="inlineStr">
+      <c r="C195" s="33" t="inlineStr">
         <is>
           <t>Фланцевая проходная</t>
         </is>
       </c>
-      <c r="D195" s="26" t="n"/>
-      <c r="E195" s="26" t="n"/>
-      <c r="F195" s="26" t="n"/>
-      <c r="G195" s="26" t="n">
+      <c r="D195" s="32" t="n"/>
+      <c r="E195" s="32" t="n"/>
+      <c r="F195" s="32" t="n"/>
+      <c r="G195" s="32" t="n">
         <v>33</v>
       </c>
-      <c r="H195" s="28" t="n">
+      <c r="H195" s="34" t="n">
         <v>588</v>
       </c>
-      <c r="I195" s="26" t="n">
+      <c r="I195" s="32" t="n">
         <v>0.67</v>
       </c>
     </row>
@@ -26095,31 +26964,31 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="26" t="inlineStr">
+      <c r="A203" s="32" t="inlineStr">
         <is>
           <t>ЯЩИК 14</t>
         </is>
       </c>
-      <c r="B203" s="26" t="inlineStr">
+      <c r="B203" s="32" t="inlineStr">
         <is>
           <t>Нижний ярус ящиков</t>
         </is>
       </c>
-      <c r="C203" s="27" t="inlineStr">
+      <c r="C203" s="33" t="inlineStr">
         <is>
           <t>Головки вентиляционные, Захлопки, Колонка смотровая, Краны, Пусковые клапаны, Редукционные клапаны, Стаканы переборочные</t>
         </is>
       </c>
-      <c r="D203" s="26" t="n"/>
-      <c r="E203" s="26" t="n"/>
-      <c r="F203" s="26" t="n"/>
-      <c r="G203" s="26" t="n">
+      <c r="D203" s="32" t="n"/>
+      <c r="E203" s="32" t="n"/>
+      <c r="F203" s="32" t="n"/>
+      <c r="G203" s="32" t="n">
         <v>137</v>
       </c>
-      <c r="H203" s="28" t="n">
+      <c r="H203" s="34" t="n">
         <v>581</v>
       </c>
-      <c r="I203" s="26" t="n">
+      <c r="I203" s="32" t="n">
         <v>0.85</v>
       </c>
     </row>
@@ -26767,31 +27636,31 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="26" t="inlineStr">
+      <c r="A225" s="32" t="inlineStr">
         <is>
           <t>ЯЩИК 15</t>
         </is>
       </c>
-      <c r="B225" s="26" t="inlineStr">
+      <c r="B225" s="32" t="inlineStr">
         <is>
           <t>Нижний ярус ящиков</t>
         </is>
       </c>
-      <c r="C225" s="27" t="inlineStr">
+      <c r="C225" s="33" t="inlineStr">
         <is>
           <t>Клинкеты, Фланцевая проходная, Фланцевая, угол или проход не указан</t>
         </is>
       </c>
-      <c r="D225" s="26" t="n"/>
-      <c r="E225" s="26" t="n"/>
-      <c r="F225" s="26" t="n"/>
-      <c r="G225" s="26" t="n">
+      <c r="D225" s="32" t="n"/>
+      <c r="E225" s="32" t="n"/>
+      <c r="F225" s="32" t="n"/>
+      <c r="G225" s="32" t="n">
         <v>45</v>
       </c>
-      <c r="H225" s="28" t="n">
+      <c r="H225" s="34" t="n">
         <v>520</v>
       </c>
-      <c r="I225" s="26" t="n">
+      <c r="I225" s="32" t="n">
         <v>0.89</v>
       </c>
     </row>
@@ -27161,31 +28030,31 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="26" t="inlineStr">
+      <c r="A239" s="32" t="inlineStr">
         <is>
           <t>ЯЩИК 16</t>
         </is>
       </c>
-      <c r="B239" s="26" t="inlineStr">
+      <c r="B239" s="32" t="inlineStr">
         <is>
           <t>Нижний ярус ящиков</t>
         </is>
       </c>
-      <c r="C239" s="27" t="inlineStr">
+      <c r="C239" s="33" t="inlineStr">
         <is>
           <t>Фланцевая угловая, Штуцерная проходная, Штуцерная, угол или проход не указан</t>
         </is>
       </c>
-      <c r="D239" s="26" t="n"/>
-      <c r="E239" s="26" t="n"/>
-      <c r="F239" s="26" t="n"/>
-      <c r="G239" s="26" t="n">
+      <c r="D239" s="32" t="n"/>
+      <c r="E239" s="32" t="n"/>
+      <c r="F239" s="32" t="n"/>
+      <c r="G239" s="32" t="n">
         <v>214</v>
       </c>
-      <c r="H239" s="28" t="n">
+      <c r="H239" s="34" t="n">
         <v>405</v>
       </c>
-      <c r="I239" s="26" t="n">
+      <c r="I239" s="32" t="n">
         <v>0.9</v>
       </c>
     </row>
@@ -27676,31 +28545,31 @@
       </c>
     </row>
     <row r="256">
-      <c r="A256" s="26" t="inlineStr">
+      <c r="A256" s="32" t="inlineStr">
         <is>
           <t>ЯЩИК 17</t>
         </is>
       </c>
-      <c r="B256" s="26" t="inlineStr">
+      <c r="B256" s="32" t="inlineStr">
         <is>
           <t>Нижний ярус ящиков</t>
         </is>
       </c>
-      <c r="C256" s="27" t="inlineStr">
+      <c r="C256" s="33" t="inlineStr">
         <is>
           <t>Клинкеты</t>
         </is>
       </c>
-      <c r="D256" s="26" t="n"/>
-      <c r="E256" s="26" t="n"/>
-      <c r="F256" s="26" t="n"/>
-      <c r="G256" s="26" t="n">
+      <c r="D256" s="32" t="n"/>
+      <c r="E256" s="32" t="n"/>
+      <c r="F256" s="32" t="n"/>
+      <c r="G256" s="32" t="n">
         <v>20</v>
       </c>
-      <c r="H256" s="28" t="n">
+      <c r="H256" s="34" t="n">
         <v>383</v>
       </c>
-      <c r="I256" s="26" t="n">
+      <c r="I256" s="32" t="n">
         <v>0.9</v>
       </c>
     </row>
@@ -27732,31 +28601,31 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="26" t="inlineStr">
+      <c r="A258" s="32" t="inlineStr">
         <is>
           <t>ЯЩИК 18</t>
         </is>
       </c>
-      <c r="B258" s="26" t="inlineStr">
+      <c r="B258" s="32" t="inlineStr">
         <is>
           <t>Нижний ярус ящиков</t>
         </is>
       </c>
-      <c r="C258" s="27" t="inlineStr">
+      <c r="C258" s="33" t="inlineStr">
         <is>
           <t>Клинкеты</t>
         </is>
       </c>
-      <c r="D258" s="26" t="n"/>
-      <c r="E258" s="26" t="n"/>
-      <c r="F258" s="26" t="n"/>
-      <c r="G258" s="26" t="n">
+      <c r="D258" s="32" t="n"/>
+      <c r="E258" s="32" t="n"/>
+      <c r="F258" s="32" t="n"/>
+      <c r="G258" s="32" t="n">
         <v>22</v>
       </c>
-      <c r="H258" s="28" t="n">
+      <c r="H258" s="34" t="n">
         <v>377</v>
       </c>
-      <c r="I258" s="26" t="n">
+      <c r="I258" s="32" t="n">
         <v>0.9</v>
       </c>
     </row>
@@ -27869,31 +28738,31 @@
       </c>
     </row>
     <row r="263">
-      <c r="A263" s="26" t="inlineStr">
+      <c r="A263" s="32" t="inlineStr">
         <is>
           <t>ЯЩИК 19</t>
         </is>
       </c>
-      <c r="B263" s="26" t="inlineStr">
+      <c r="B263" s="32" t="inlineStr">
         <is>
           <t>Нижний ярус ящиков</t>
         </is>
       </c>
-      <c r="C263" s="27" t="inlineStr">
+      <c r="C263" s="33" t="inlineStr">
         <is>
           <t>Клинкеты</t>
         </is>
       </c>
-      <c r="D263" s="26" t="n"/>
-      <c r="E263" s="26" t="n"/>
-      <c r="F263" s="26" t="n"/>
-      <c r="G263" s="26" t="n">
+      <c r="D263" s="32" t="n"/>
+      <c r="E263" s="32" t="n"/>
+      <c r="F263" s="32" t="n"/>
+      <c r="G263" s="32" t="n">
         <v>30</v>
       </c>
-      <c r="H263" s="28" t="n">
+      <c r="H263" s="34" t="n">
         <v>352</v>
       </c>
-      <c r="I263" s="26" t="n">
+      <c r="I263" s="32" t="n">
         <v>0.9</v>
       </c>
     </row>
@@ -27979,31 +28848,31 @@
       </c>
     </row>
     <row r="267">
-      <c r="A267" s="26" t="inlineStr">
+      <c r="A267" s="32" t="inlineStr">
         <is>
           <t>ЯЩИК 20</t>
         </is>
       </c>
-      <c r="B267" s="26" t="inlineStr">
+      <c r="B267" s="32" t="inlineStr">
         <is>
           <t>Нижний ярус ящиков</t>
         </is>
       </c>
-      <c r="C267" s="27" t="inlineStr">
+      <c r="C267" s="33" t="inlineStr">
         <is>
           <t>Клинкеты</t>
         </is>
       </c>
-      <c r="D267" s="26" t="n"/>
-      <c r="E267" s="26" t="n"/>
-      <c r="F267" s="26" t="n"/>
-      <c r="G267" s="26" t="n">
+      <c r="D267" s="32" t="n"/>
+      <c r="E267" s="32" t="n"/>
+      <c r="F267" s="32" t="n"/>
+      <c r="G267" s="32" t="n">
         <v>30</v>
       </c>
-      <c r="H267" s="28" t="n">
+      <c r="H267" s="34" t="n">
         <v>349</v>
       </c>
-      <c r="I267" s="26" t="n">
+      <c r="I267" s="32" t="n">
         <v>0.89</v>
       </c>
     </row>
@@ -28089,31 +28958,31 @@
       </c>
     </row>
     <row r="271">
-      <c r="A271" s="26" t="inlineStr">
+      <c r="A271" s="32" t="inlineStr">
         <is>
           <t>ЯЩИК 21</t>
         </is>
       </c>
-      <c r="B271" s="26" t="inlineStr">
+      <c r="B271" s="32" t="inlineStr">
         <is>
           <t>Нижний ярус ящиков</t>
         </is>
       </c>
-      <c r="C271" s="27" t="inlineStr">
+      <c r="C271" s="33" t="inlineStr">
         <is>
           <t>Без описания — уточнить, Педальные клапаны, Эжекторы</t>
         </is>
       </c>
-      <c r="D271" s="26" t="n"/>
-      <c r="E271" s="26" t="n"/>
-      <c r="F271" s="26" t="n"/>
-      <c r="G271" s="26" t="n">
+      <c r="D271" s="32" t="n"/>
+      <c r="E271" s="32" t="n"/>
+      <c r="F271" s="32" t="n"/>
+      <c r="G271" s="32" t="n">
         <v>23</v>
       </c>
-      <c r="H271" s="28" t="n">
+      <c r="H271" s="34" t="n">
         <v>121</v>
       </c>
-      <c r="I271" s="26" t="n">
+      <c r="I271" s="32" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -28317,31 +29186,31 @@
       </c>
     </row>
     <row r="279">
-      <c r="A279" s="26" t="inlineStr">
+      <c r="A279" s="32" t="inlineStr">
         <is>
           <t>ЯЩИК 22</t>
         </is>
       </c>
-      <c r="B279" s="26" t="inlineStr">
+      <c r="B279" s="32" t="inlineStr">
         <is>
           <t>Нижний ярус ящиков</t>
         </is>
       </c>
-      <c r="C279" s="27" t="inlineStr">
+      <c r="C279" s="33" t="inlineStr">
         <is>
           <t>Головки вентиляционные, Кингстоны, Фильтры забортной воды</t>
         </is>
       </c>
-      <c r="D279" s="26" t="n"/>
-      <c r="E279" s="26" t="n"/>
-      <c r="F279" s="26" t="n"/>
-      <c r="G279" s="26" t="n">
+      <c r="D279" s="32" t="n"/>
+      <c r="E279" s="32" t="n"/>
+      <c r="F279" s="32" t="n"/>
+      <c r="G279" s="32" t="n">
         <v>22</v>
       </c>
-      <c r="H279" s="28" t="n">
+      <c r="H279" s="34" t="n">
         <v>596</v>
       </c>
-      <c r="I279" s="26" t="n">
+      <c r="I279" s="32" t="n">
         <v>0.87</v>
       </c>
     </row>
@@ -28648,31 +29517,31 @@
       </c>
     </row>
     <row r="290">
-      <c r="A290" s="26" t="inlineStr">
+      <c r="A290" s="32" t="inlineStr">
         <is>
           <t>ЯЩИК 23</t>
         </is>
       </c>
-      <c r="B290" s="26" t="inlineStr">
+      <c r="B290" s="32" t="inlineStr">
         <is>
           <t>Верхний ярус ящиков</t>
         </is>
       </c>
-      <c r="C290" s="27" t="inlineStr">
+      <c r="C290" s="33" t="inlineStr">
         <is>
           <t>Фильтры забортной воды</t>
         </is>
       </c>
-      <c r="D290" s="26" t="n"/>
-      <c r="E290" s="26" t="n"/>
-      <c r="F290" s="26" t="n"/>
-      <c r="G290" s="26" t="n">
+      <c r="D290" s="32" t="n"/>
+      <c r="E290" s="32" t="n"/>
+      <c r="F290" s="32" t="n"/>
+      <c r="G290" s="32" t="n">
         <v>4</v>
       </c>
-      <c r="H290" s="28" t="n">
+      <c r="H290" s="34" t="n">
         <v>592</v>
       </c>
-      <c r="I290" s="26" t="n">
+      <c r="I290" s="32" t="n">
         <v>0.64</v>
       </c>
     </row>
@@ -28704,31 +29573,31 @@
       </c>
     </row>
     <row r="292">
-      <c r="A292" s="26" t="inlineStr">
+      <c r="A292" s="32" t="inlineStr">
         <is>
           <t>ЯЩИК 24</t>
         </is>
       </c>
-      <c r="B292" s="26" t="inlineStr">
+      <c r="B292" s="32" t="inlineStr">
         <is>
           <t>Верхний ярус ящиков</t>
         </is>
       </c>
-      <c r="C292" s="27" t="inlineStr">
+      <c r="C292" s="33" t="inlineStr">
         <is>
           <t>Фильтры забортной воды</t>
         </is>
       </c>
-      <c r="D292" s="26" t="n"/>
-      <c r="E292" s="26" t="n"/>
-      <c r="F292" s="26" t="n"/>
-      <c r="G292" s="26" t="n">
+      <c r="D292" s="32" t="n"/>
+      <c r="E292" s="32" t="n"/>
+      <c r="F292" s="32" t="n"/>
+      <c r="G292" s="32" t="n">
         <v>13</v>
       </c>
-      <c r="H292" s="28" t="n">
+      <c r="H292" s="34" t="n">
         <v>540</v>
       </c>
-      <c r="I292" s="26" t="n">
+      <c r="I292" s="32" t="n">
         <v>0.65</v>
       </c>
     </row>
@@ -28899,31 +29768,31 @@
       </c>
     </row>
     <row r="299">
-      <c r="A299" s="26" t="inlineStr">
+      <c r="A299" s="32" t="inlineStr">
         <is>
           <t>ЯЩИК 25</t>
         </is>
       </c>
-      <c r="B299" s="26" t="inlineStr">
+      <c r="B299" s="32" t="inlineStr">
         <is>
           <t>Верхний ярус ящиков</t>
         </is>
       </c>
-      <c r="C299" s="27" t="inlineStr">
+      <c r="C299" s="33" t="inlineStr">
         <is>
           <t>Фильтры забортной воды</t>
         </is>
       </c>
-      <c r="D299" s="26" t="n"/>
-      <c r="E299" s="26" t="n"/>
-      <c r="F299" s="26" t="n"/>
-      <c r="G299" s="26" t="n">
+      <c r="D299" s="32" t="n"/>
+      <c r="E299" s="32" t="n"/>
+      <c r="F299" s="32" t="n"/>
+      <c r="G299" s="32" t="n">
         <v>5</v>
       </c>
-      <c r="H299" s="28" t="n">
+      <c r="H299" s="34" t="n">
         <v>488</v>
       </c>
-      <c r="I299" s="26" t="n">
+      <c r="I299" s="32" t="n">
         <v>0.62</v>
       </c>
     </row>
@@ -28982,31 +29851,31 @@
       </c>
     </row>
     <row r="302">
-      <c r="A302" s="26" t="inlineStr">
+      <c r="A302" s="32" t="inlineStr">
         <is>
           <t>ЯЩИК 26</t>
         </is>
       </c>
-      <c r="B302" s="26" t="inlineStr">
+      <c r="B302" s="32" t="inlineStr">
         <is>
           <t>Верхний ярус ящиков</t>
         </is>
       </c>
-      <c r="C302" s="27" t="inlineStr">
+      <c r="C302" s="33" t="inlineStr">
         <is>
           <t>Клинкеты, Фильтры забортной воды</t>
         </is>
       </c>
-      <c r="D302" s="26" t="n"/>
-      <c r="E302" s="26" t="n"/>
-      <c r="F302" s="26" t="n"/>
-      <c r="G302" s="26" t="n">
+      <c r="D302" s="32" t="n"/>
+      <c r="E302" s="32" t="n"/>
+      <c r="F302" s="32" t="n"/>
+      <c r="G302" s="32" t="n">
         <v>23</v>
       </c>
-      <c r="H302" s="28" t="n">
+      <c r="H302" s="34" t="n">
         <v>438</v>
       </c>
-      <c r="I302" s="26" t="n">
+      <c r="I302" s="32" t="n">
         <v>0.89</v>
       </c>
     </row>
@@ -29244,7 +30113,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -29424,7 +30293,7 @@
           <t>Чистый объем доски, куб. м</t>
         </is>
       </c>
-      <c r="B16" s="29" t="n">
+      <c r="B16" s="35" t="n">
         <v>1.09</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -29439,7 +30308,7 @@
           <t>С запасом на обзол и подгонку, куб. м</t>
         </is>
       </c>
-      <c r="B17" s="29" t="n">
+      <c r="B17" s="35" t="n">
         <v>1.36</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -29518,7 +30387,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/outputs/marine_equipment/Контейнер_40ф_Питер.xlsx
+++ b/outputs/marine_equipment/Контейнер_40ф_Питер.xlsx
@@ -19948,7 +19948,11 @@
       <c r="J7" s="21" t="n">
         <v>0.13</v>
       </c>
-      <c r="K7" s="14" t="inlineStr"/>
+      <c r="K7" s="24" t="inlineStr">
+        <is>
+          <t>сталь</t>
+        </is>
+      </c>
       <c r="L7" s="23" t="inlineStr">
         <is>
           <t>Б. Добор со склада</t>
